--- a/event_planner_forms/002_zoom_webinar_registration_form--event_planner_forms.xlsx
+++ b/event_planner_forms/002_zoom_webinar_registration_form--event_planner_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>time zone</t>
+          <t>Timezone</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>timezone_offset</t>
+          <t>timezone_offset_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>time zone offset</t>
+          <t>Timezone Offset 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>timezone</t>
+          <t>timezone_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>time zone</t>
+          <t>Timezone 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>time zone offset</t>
+          <t>Timezone Offset Label</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>start_time</t>
+          <t>start_time_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>start time</t>
+          <t>Start Time 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>end_time</t>
+          <t>end_time_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>end time</t>
+          <t>End Time 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -960,10 +960,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C136"/>
+  <dimension ref="A1:C126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
@@ -2246,1035 +2246,865 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_2_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_2_choices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_2_choices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>start_time_2_choices</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>08:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>start_time_2_choices</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>09:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>start_time_2_choices</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>600</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>600</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>start_time_2_choices</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>660</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>660</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>start_time_2_choices</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>720</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>720</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>start_time_2_choices</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>780</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>780</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>start_time_2_choices</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>840</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>840</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>start_time_2_choices</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>900</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>900</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>start_time_2_choices</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>960</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>960</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>start_time_2_choices</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1020</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>start_time_choices</t>
+          <t>start_time_2_choices</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>1080</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>start_time_choices</t>
+          <t>start_time_2_choices</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>1140</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>start_time_choices</t>
+          <t>start_time_2_choices</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1200</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>start_time_choices</t>
+          <t>start_time_2_choices</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>1260</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>start_time_choices</t>
+          <t>start_time_2_choices</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>1320</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>start_time_choices</t>
+          <t>start_time_2_choices</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>1380</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>start_time_choices</t>
+          <t>start_time_2_choices</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>00:00</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>start_time_choices</t>
+          <t>start_time_2_choices</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>01:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>start_time_choices</t>
+          <t>start_time_2_choices</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>02:00</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>start_time_choices</t>
+          <t>start_time_2_choices</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>03:00</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>start_time_choices</t>
+          <t>start_time_2_choices</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>04:00</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>start_time_choices</t>
+          <t>start_time_2_choices</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>05:00</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>start_time_choices</t>
+          <t>start_time_2_choices</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>06:00</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>start_time_choices</t>
+          <t>start_time_2_choices</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>07:00</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>start_time_choices</t>
+          <t>end_time_2_choices</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>08:00</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>start_time_choices</t>
+          <t>end_time_2_choices</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>09:00</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>start_time_choices</t>
+          <t>end_time_2_choices</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>600</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>600</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>start_time_choices</t>
+          <t>end_time_2_choices</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>660</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>660</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>start_time_choices</t>
+          <t>end_time_2_choices</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>720</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>720</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>start_time_choices</t>
+          <t>end_time_2_choices</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>780</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>780</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>start_time_choices</t>
+          <t>end_time_2_choices</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>840</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>840</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>start_time_choices</t>
+          <t>end_time_2_choices</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>900</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>900</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>start_time_choices</t>
+          <t>end_time_2_choices</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>960</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>960</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>start_time_choices</t>
+          <t>end_time_2_choices</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>1020</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>end_time_choices</t>
+          <t>end_time_2_choices</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>1080</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>end_time_choices</t>
+          <t>end_time_2_choices</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>1140</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>end_time_choices</t>
+          <t>end_time_2_choices</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1200</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>end_time_choices</t>
+          <t>end_time_2_choices</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>1260</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>end_time_choices</t>
+          <t>end_time_2_choices</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>1320</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>end_time_choices</t>
+          <t>end_time_2_choices</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>1380</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>end_time_choices</t>
+          <t>end_time_2_choices</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>00:00</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>end_time_choices</t>
+          <t>end_time_2_choices</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>01:00</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>end_time_choices</t>
+          <t>end_time_2_choices</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>02:00</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>end_time_choices</t>
+          <t>end_time_2_choices</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>03:00</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>end_time_choices</t>
+          <t>end_time_2_choices</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>04:00</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>end_time_choices</t>
+          <t>end_time_2_choices</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>05:00</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>end_time_choices</t>
+          <t>end_time_2_choices</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>06:00</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>end_time_choices</t>
+          <t>end_time_2_choices</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>end_time_choices</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>1320</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>1320</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>end_time_choices</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>1380</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>1380</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>end_time_choices</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>end_time_choices</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>01:00</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>01:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>end_time_choices</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>02:00</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>02:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>end_time_choices</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>03:00</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>end_time_choices</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>end_time_choices</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>end_time_choices</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>end_time_choices</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
